--- a/results/metrics_gc.xlsx
+++ b/results/metrics_gc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dalhousie\Desktop\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D34B887-4CE7-4DCE-A3AE-4E75A983BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0AA35F-2DFE-4838-B4D6-58FCD90A094C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4CFA2B7B-2954-452C-B3E8-39BCF96D755A}"/>
   </bookViews>
@@ -5943,7 +5943,7 @@
         <v>119</v>
       </c>
       <c r="E2" s="3">
-        <v>56383</v>
+        <v>1564</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>121</v>
       </c>
       <c r="E3" s="3">
-        <v>6061</v>
+        <v>853</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -6007,7 +6007,7 @@
         <v>122</v>
       </c>
       <c r="E4" s="3">
-        <v>26660</v>
+        <v>698</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -6039,7 +6039,7 @@
         <v>124</v>
       </c>
       <c r="E5" s="3">
-        <v>10887</v>
+        <v>3641</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>126</v>
       </c>
       <c r="E6" s="3">
-        <v>1227</v>
+        <v>521</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -6103,7 +6103,7 @@
         <v>127</v>
       </c>
       <c r="E7" s="3">
-        <v>26884</v>
+        <v>1992</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -6135,7 +6135,7 @@
         <v>128</v>
       </c>
       <c r="E8" s="3">
-        <v>11118</v>
+        <v>1370</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>129</v>
       </c>
       <c r="E9" s="3">
-        <v>9721</v>
+        <v>3405</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="E10" s="3">
-        <v>3439</v>
+        <v>745</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         <v>132</v>
       </c>
       <c r="E11" s="3">
-        <v>3744</v>
+        <v>1004</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
@@ -6263,7 +6263,7 @@
         <v>133</v>
       </c>
       <c r="E12" s="3">
-        <v>311</v>
+        <v>428</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>135</v>
       </c>
       <c r="E13" s="3">
-        <v>6036</v>
+        <v>1377</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>136</v>
       </c>
       <c r="E14" s="3">
-        <v>4052</v>
+        <v>1382</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -6359,7 +6359,7 @@
         <v>137</v>
       </c>
       <c r="E15" s="3">
-        <v>2102</v>
+        <v>1251</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -6391,7 +6391,7 @@
         <v>138</v>
       </c>
       <c r="E16" s="3">
-        <v>1222</v>
+        <v>620</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>139</v>
       </c>
       <c r="E17" s="3">
-        <v>29335</v>
+        <v>4385</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -6455,7 +6455,7 @@
         <v>140</v>
       </c>
       <c r="E18" s="3">
-        <v>6355</v>
+        <v>872</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>141</v>
       </c>
       <c r="E19" s="3">
-        <v>31273</v>
+        <v>4675</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -6519,7 +6519,7 @@
         <v>142</v>
       </c>
       <c r="E20" s="3">
-        <v>30697</v>
+        <v>5325</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -6551,7 +6551,7 @@
         <v>143</v>
       </c>
       <c r="E21" s="3">
-        <v>29411</v>
+        <v>5618</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -6583,7 +6583,7 @@
         <v>144</v>
       </c>
       <c r="E22" s="3">
-        <v>18747</v>
+        <v>3490</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>145</v>
       </c>
       <c r="E23" s="3">
-        <v>475</v>
+        <v>726</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         <v>147</v>
       </c>
       <c r="E24" s="3">
-        <v>14543</v>
+        <v>4519</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -6679,7 +6679,7 @@
         <v>148</v>
       </c>
       <c r="E25" s="3">
-        <v>16042</v>
+        <v>886</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>149</v>
       </c>
       <c r="E26" s="3">
-        <v>9104</v>
+        <v>1700</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -6743,7 +6743,7 @@
         <v>150</v>
       </c>
       <c r="E27" s="3">
-        <v>25972</v>
+        <v>4808</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -6775,7 +6775,7 @@
         <v>151</v>
       </c>
       <c r="E28" s="3">
-        <v>715</v>
+        <v>457</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>152</v>
       </c>
       <c r="E29" s="3">
-        <v>283</v>
+        <v>415</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>153</v>
       </c>
       <c r="E30" s="3">
-        <v>86828</v>
+        <v>7509</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -6871,7 +6871,7 @@
         <v>154</v>
       </c>
       <c r="E31" s="3">
-        <v>19018</v>
+        <v>1457</v>
       </c>
       <c r="F31" s="3">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>155</v>
       </c>
       <c r="E32" s="3">
-        <v>1876</v>
+        <v>850</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -6935,7 +6935,7 @@
         <v>156</v>
       </c>
       <c r="E33" s="3">
-        <v>328</v>
+        <v>1109</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>157</v>
       </c>
       <c r="E34" s="3">
-        <v>558</v>
+        <v>462</v>
       </c>
       <c r="F34" s="3">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>158</v>
       </c>
       <c r="E35" s="3">
-        <v>2056</v>
+        <v>601</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
@@ -7031,7 +7031,7 @@
         <v>159</v>
       </c>
       <c r="E36" s="3">
-        <v>1858</v>
+        <v>671</v>
       </c>
       <c r="F36" s="3">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>160</v>
       </c>
       <c r="E37" s="3">
-        <v>48871</v>
+        <v>10148</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -7095,7 +7095,7 @@
         <v>162</v>
       </c>
       <c r="E38" s="3">
-        <v>3757</v>
+        <v>869</v>
       </c>
       <c r="F38" s="3">
         <v>0</v>
@@ -7127,7 +7127,7 @@
         <v>163</v>
       </c>
       <c r="E39" s="3">
-        <v>23328</v>
+        <v>4525</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
@@ -7159,7 +7159,7 @@
         <v>165</v>
       </c>
       <c r="E40" s="3">
-        <v>82548</v>
+        <v>4579</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
@@ -7191,7 +7191,7 @@
         <v>166</v>
       </c>
       <c r="E41" s="3">
-        <v>1825</v>
+        <v>713</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>167</v>
       </c>
       <c r="E42" s="3">
-        <v>2636</v>
+        <v>789</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -7255,7 +7255,7 @@
         <v>168</v>
       </c>
       <c r="E43" s="3">
-        <v>10506</v>
+        <v>845</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>169</v>
       </c>
       <c r="E44" s="3">
-        <v>18107</v>
+        <v>3798</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -7319,7 +7319,7 @@
         <v>170</v>
       </c>
       <c r="E45" s="3">
-        <v>4278</v>
+        <v>1983</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -7351,7 +7351,7 @@
         <v>171</v>
       </c>
       <c r="E46" s="3">
-        <v>3112</v>
+        <v>583</v>
       </c>
       <c r="F46" s="3">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>172</v>
       </c>
       <c r="E47" s="3">
-        <v>47496</v>
+        <v>4990</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
@@ -7415,7 +7415,7 @@
         <v>173</v>
       </c>
       <c r="E48" s="3">
-        <v>6948</v>
+        <v>1240</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
@@ -7447,7 +7447,7 @@
         <v>174</v>
       </c>
       <c r="E49" s="3">
-        <v>1233</v>
+        <v>3869</v>
       </c>
       <c r="F49" s="3">
         <v>1</v>
@@ -7479,7 +7479,7 @@
         <v>175</v>
       </c>
       <c r="E50" s="3">
-        <v>5611</v>
+        <v>814</v>
       </c>
       <c r="F50" s="3">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>176</v>
       </c>
       <c r="E51" s="3">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
@@ -7543,7 +7543,7 @@
         <v>177</v>
       </c>
       <c r="E52" s="3">
-        <v>12974</v>
+        <v>823</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>178</v>
       </c>
       <c r="E53" s="3">
-        <v>9569</v>
+        <v>1127</v>
       </c>
       <c r="F53" s="3">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         <v>179</v>
       </c>
       <c r="E54" s="3">
-        <v>14121</v>
+        <v>1390</v>
       </c>
       <c r="F54" s="3">
         <v>0</v>
@@ -7639,7 +7639,7 @@
         <v>180</v>
       </c>
       <c r="E55" s="3">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
@@ -7671,7 +7671,7 @@
         <v>182</v>
       </c>
       <c r="E56" s="3">
-        <v>317</v>
+        <v>716</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -7703,7 +7703,7 @@
         <v>183</v>
       </c>
       <c r="E57" s="3">
-        <v>31698</v>
+        <v>2616</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>184</v>
       </c>
       <c r="E58" s="3">
-        <v>98414</v>
+        <v>7731</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
@@ -7767,7 +7767,7 @@
         <v>185</v>
       </c>
       <c r="E59" s="3">
-        <v>42308</v>
+        <v>1556</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -7799,7 +7799,7 @@
         <v>186</v>
       </c>
       <c r="E60" s="3">
-        <v>26451</v>
+        <v>1759</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>187</v>
       </c>
       <c r="E61" s="3">
-        <v>43400</v>
+        <v>6781</v>
       </c>
       <c r="F61" s="3">
         <v>1</v>
@@ -7863,7 +7863,7 @@
         <v>188</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>696</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -7895,7 +7895,7 @@
         <v>189</v>
       </c>
       <c r="E63" s="3">
-        <v>27967</v>
+        <v>2754</v>
       </c>
       <c r="F63" s="3">
         <v>1</v>
@@ -7927,7 +7927,7 @@
         <v>190</v>
       </c>
       <c r="E64" s="3">
-        <v>804</v>
+        <v>2226</v>
       </c>
       <c r="F64" s="3">
         <v>0</v>
@@ -7959,7 +7959,7 @@
         <v>191</v>
       </c>
       <c r="E65" s="3">
-        <v>49767</v>
+        <v>5347</v>
       </c>
       <c r="F65" s="3">
         <v>0</v>
@@ -7991,7 +7991,7 @@
         <v>192</v>
       </c>
       <c r="E66" s="3">
-        <v>10226</v>
+        <v>1496</v>
       </c>
       <c r="F66" s="3">
         <v>1</v>
@@ -8023,7 +8023,7 @@
         <v>193</v>
       </c>
       <c r="E67" s="3">
-        <v>37491</v>
+        <v>1725</v>
       </c>
       <c r="F67" s="3">
         <v>0</v>
@@ -8055,7 +8055,7 @@
         <v>194</v>
       </c>
       <c r="E68" s="3">
-        <v>1094</v>
+        <v>546</v>
       </c>
       <c r="F68" s="3">
         <v>0</v>
@@ -8087,7 +8087,7 @@
         <v>195</v>
       </c>
       <c r="E69" s="3">
-        <v>291</v>
+        <v>555</v>
       </c>
       <c r="F69" s="3">
         <v>0</v>
@@ -8119,7 +8119,7 @@
         <v>196</v>
       </c>
       <c r="E70" s="3">
-        <v>17798</v>
+        <v>2302</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -8151,7 +8151,7 @@
         <v>197</v>
       </c>
       <c r="E71" s="3">
-        <v>15499</v>
+        <v>13835</v>
       </c>
       <c r="F71" s="3">
         <v>1</v>
@@ -8183,7 +8183,7 @@
         <v>198</v>
       </c>
       <c r="E72" s="3">
-        <v>53375</v>
+        <v>5116</v>
       </c>
       <c r="F72" s="3">
         <v>1</v>
@@ -8215,7 +8215,7 @@
         <v>199</v>
       </c>
       <c r="E73" s="3">
-        <v>2732</v>
+        <v>1003</v>
       </c>
       <c r="F73" s="3">
         <v>0</v>
@@ -8247,7 +8247,7 @@
         <v>200</v>
       </c>
       <c r="E74" s="3">
-        <v>81567</v>
+        <v>4989</v>
       </c>
       <c r="F74" s="3">
         <v>1</v>
@@ -8279,7 +8279,7 @@
         <v>201</v>
       </c>
       <c r="E75" s="3">
-        <v>4014</v>
+        <v>442</v>
       </c>
       <c r="F75" s="3">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>202</v>
       </c>
       <c r="E76" s="3">
-        <v>4452</v>
+        <v>925</v>
       </c>
       <c r="F76" s="3">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>203</v>
       </c>
       <c r="E77" s="3">
-        <v>68316</v>
+        <v>5480</v>
       </c>
       <c r="F77" s="3">
         <v>1</v>
@@ -8375,7 +8375,7 @@
         <v>204</v>
       </c>
       <c r="E78" s="3">
-        <v>23606</v>
+        <v>981</v>
       </c>
       <c r="F78" s="3">
         <v>0</v>
@@ -8407,7 +8407,7 @@
         <v>205</v>
       </c>
       <c r="E79" s="3">
-        <v>83237</v>
+        <v>5522</v>
       </c>
       <c r="F79" s="3">
         <v>1</v>
@@ -8439,7 +8439,7 @@
         <v>206</v>
       </c>
       <c r="E80" s="3">
-        <v>709</v>
+        <v>635</v>
       </c>
       <c r="F80" s="3">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         <v>207</v>
       </c>
       <c r="E81" s="3">
-        <v>3875</v>
+        <v>1138</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>208</v>
       </c>
       <c r="E82" s="3">
-        <v>446</v>
+        <v>509</v>
       </c>
       <c r="F82" s="3">
         <v>0</v>
@@ -8535,7 +8535,7 @@
         <v>209</v>
       </c>
       <c r="E83" s="3">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -8567,7 +8567,7 @@
         <v>210</v>
       </c>
       <c r="E84" s="3">
-        <v>90858</v>
+        <v>19348</v>
       </c>
       <c r="F84" s="3">
         <v>1</v>
@@ -8599,7 +8599,7 @@
         <v>211</v>
       </c>
       <c r="E85" s="3">
-        <v>5207</v>
+        <v>906</v>
       </c>
       <c r="F85" s="3">
         <v>0</v>
@@ -8631,7 +8631,7 @@
         <v>212</v>
       </c>
       <c r="E86" s="3">
-        <v>839</v>
+        <v>428</v>
       </c>
       <c r="F86" s="3">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>213</v>
       </c>
       <c r="E87" s="3">
-        <v>1447</v>
+        <v>794</v>
       </c>
       <c r="F87" s="3">
         <v>0</v>
@@ -8695,7 +8695,7 @@
         <v>214</v>
       </c>
       <c r="E88" s="3">
-        <v>71343</v>
+        <v>4331</v>
       </c>
       <c r="F88" s="3">
         <v>1</v>
@@ -8727,7 +8727,7 @@
         <v>215</v>
       </c>
       <c r="E89" s="3">
-        <v>23188</v>
+        <v>1129</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         <v>216</v>
       </c>
       <c r="E90" s="3">
-        <v>4081</v>
+        <v>1204</v>
       </c>
       <c r="F90" s="3">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>217</v>
       </c>
       <c r="E91" s="3">
-        <v>3305</v>
+        <v>803</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8823,7 +8823,7 @@
         <v>218</v>
       </c>
       <c r="E92" s="3">
-        <v>5445</v>
+        <v>691</v>
       </c>
       <c r="F92" s="3">
         <v>0</v>
@@ -8855,7 +8855,7 @@
         <v>219</v>
       </c>
       <c r="E93" s="3">
-        <v>14367</v>
+        <v>2217</v>
       </c>
       <c r="F93" s="3">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         <v>220</v>
       </c>
       <c r="E94" s="3">
-        <v>3682</v>
+        <v>1081</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>221</v>
       </c>
       <c r="E95" s="3">
-        <v>76713</v>
+        <v>6568</v>
       </c>
       <c r="F95" s="3">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>222</v>
       </c>
       <c r="E96" s="3">
-        <v>83259</v>
+        <v>4258</v>
       </c>
       <c r="F96" s="3">
         <v>1</v>
@@ -8983,7 +8983,7 @@
         <v>223</v>
       </c>
       <c r="E97" s="3">
-        <v>9480</v>
+        <v>1093</v>
       </c>
       <c r="F97" s="3">
         <v>0</v>
@@ -9015,7 +9015,7 @@
         <v>224</v>
       </c>
       <c r="E98" s="3">
-        <v>53058</v>
+        <v>2108</v>
       </c>
       <c r="F98" s="3">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>225</v>
       </c>
       <c r="E99" s="3">
-        <v>35141</v>
+        <v>1048</v>
       </c>
       <c r="F99" s="3">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>226</v>
       </c>
       <c r="E100" s="3">
-        <v>30345</v>
+        <v>4104</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
@@ -9111,7 +9111,7 @@
         <v>227</v>
       </c>
       <c r="E101" s="3">
-        <v>16704</v>
+        <v>2507</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -9130,7 +9130,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I101" xr:uid="{89F89906-325E-45A3-964D-C321123BF65D}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
